--- a/data/trans_orig/IP1021_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1021_2023-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>602</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6509</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98586</t>
+          <t>98566</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104075</t>
+          <t>103734</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130033</t>
+          <t>129864</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135779</t>
+          <t>135771</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>231918</t>
+          <t>230799</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239198</t>
+          <t>239143</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>421</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89849</t>
+          <t>89709</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94259</t>
+          <t>94260</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88456</t>
+          <t>88313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>181135</t>
+          <t>181225</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188946</t>
+          <t>188967</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49844</t>
+          <t>49863</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57963</t>
+          <t>58571</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109849</t>
+          <t>110168</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115328</t>
+          <t>115356</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>816</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10554</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>211408</t>
+          <t>211240</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217363</t>
+          <t>217355</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>210566</t>
+          <t>211410</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>217454</t>
+          <t>217456</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>425728</t>
+          <t>426590</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>433981</t>
+          <t>433969</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109649</t>
+          <t>109718</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117046</t>
+          <t>116732</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155360</t>
+          <t>154929</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161960</t>
+          <t>161939</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>268423</t>
+          <t>268168</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278176</t>
+          <t>277726</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>393</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64552</t>
+          <t>65004</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65277</t>
+          <t>65589</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>133077</t>
+          <t>132129</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>140502</t>
+          <t>140505</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19026</t>
+          <t>20603</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21345</t>
+          <t>21141</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18123</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>36586</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>638311</t>
+          <t>636734</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>649372</t>
+          <t>648749</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>727345</t>
+          <t>727549</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>740999</t>
+          <t>741145</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1370785</t>
+          <t>1369441</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1387904</t>
+          <t>1387523</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1021_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1021_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>522</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>346</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6509</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>119922</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>115854</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>121496</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,28%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>102466</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>98566</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>103734</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,36%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>134057</t>
+          <t>100923</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129864</t>
+          <t>96613</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135771</t>
+          <t>102581</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>236522</t>
+          <t>220846</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>230799</t>
+          <t>216093</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239143</t>
+          <t>223459</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122018</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122018</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122018</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136373</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136373</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136373</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>240834</t>
+          <t>224946</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>240834</t>
+          <t>224946</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>240834</t>
+          <t>224946</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6475</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4972</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>352</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>89429</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>84923</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>92881</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>89709</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>94260</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>93437</t>
+          <t>94781</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88313</t>
+          <t>91355</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96194</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>186318</t>
+          <t>184210</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>181225</t>
+          <t>179098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188967</t>
+          <t>186545</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5250</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1776</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1563</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5282</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>354</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -1519,74 +1519,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>55506</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>51691</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,78%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>51476</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>49863</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>53138</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>51706</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>53482</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,68%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>62290</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>58571</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>63853</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>91,73%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>156</t>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>113766</t>
+          <t>108644</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110168</t>
+          <t>104547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115356</t>
+          <t>110069</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>689</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>734</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,22 +1824,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>199604</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>195526</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>201255</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>273</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>215545</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>211240</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>217355</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,89%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>215625</t>
+          <t>176241</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>211410</t>
+          <t>172269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>217456</t>
+          <t>178079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>431170</t>
+          <t>375846</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>426590</t>
+          <t>370951</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>433969</t>
+          <t>378731</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2445</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5308</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2696</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9710</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,22 +2167,22 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>145798</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>140966</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>147689</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>114120</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>109718</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>116732</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>95,56%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>159902</t>
+          <t>113286</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154929</t>
+          <t>108556</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161939</t>
+          <t>116152</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,27 +2280,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>274023</t>
+          <t>259084</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>268168</t>
+          <t>253215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>277726</t>
+          <t>262884</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6372</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>9,33%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3891</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3952</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6414</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>346</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>6657</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -2548,74 +2548,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67309</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>61915</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>90,67%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>67765</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>65004</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>98,36%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>94,35%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>69249</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>66404</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>70356</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>94,38%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>70636</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>65589</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>72003</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>91,09%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>186</t>
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>138402</t>
+          <t>136559</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>132129</t>
+          <t>131987</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>140505</t>
+          <t>138298</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11263</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6336</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>18640</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>13084</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>8588</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>20603</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21141</t>
+          <t>20381</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>25827</t>
+          <t>24500</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>16963</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36586</t>
+          <t>34160</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>677568</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>670191</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>682495</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>907</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>644253</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>636734</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>648749</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>943</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>735947</t>
+          <t>607621</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>727549</t>
+          <t>600476</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>741145</t>
+          <t>612504</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1380200</t>
+          <t>1285188</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1369441</t>
+          <t>1275528</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1387523</t>
+          <t>1292725</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>688831</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>688831</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>688831</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>657337</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>657337</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>657337</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>958</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>748690</t>
+          <t>620857</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>748690</t>
+          <t>620857</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>748690</t>
+          <t>620857</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1406027</t>
+          <t>1309688</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1406027</t>
+          <t>1309688</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1406027</t>
+          <t>1309688</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
